--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,327 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129700100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96004</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>308670</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6423944</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129700307</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>308670</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6423944</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129700439</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96004</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>308673</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6423874</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>96005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R4" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>96004</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R5" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B4" t="n">
-        <v>96010</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R4" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>96014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R5" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>96016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R4" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>96014</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R5" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B4" t="n">
-        <v>96016</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R4" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>96016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R5" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>96016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R4" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>96016</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R5" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B4" t="n">
-        <v>96030</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R4" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>96030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R5" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>96033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R4" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>96030</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R5" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B4" t="n">
-        <v>96034</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R4" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>96034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R5" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129700100</v>
       </c>
       <c r="B3" t="n">
-        <v>96034</v>
+        <v>96051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>96051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R4" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>96034</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R5" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127099409</v>
       </c>
       <c r="B2" t="n">
-        <v>97550</v>
+        <v>97520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127099409</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127099409</v>
+        <v>129700100</v>
       </c>
       <c r="B2" t="n">
-        <v>97550</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lokullemossen, Boh</t>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>308747</v>
+        <v>308670</v>
       </c>
       <c r="R2" t="n">
-        <v>6423910</v>
+        <v>6423944</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundström, Maria Aronsson, tomas aronsson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129700100</v>
+        <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96056</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>308670</v>
+        <v>308663</v>
       </c>
       <c r="R3" t="n">
-        <v>6423944</v>
+        <v>6423899</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129700307</v>
+        <v>129700439</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>308670</v>
+        <v>308673</v>
       </c>
       <c r="R4" t="n">
-        <v>6423944</v>
+        <v>6423874</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129700439</v>
+        <v>129700307</v>
       </c>
       <c r="B5" t="n">
-        <v>96056</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>308673</v>
+        <v>308670</v>
       </c>
       <c r="R5" t="n">
-        <v>6423874</v>
+        <v>6423944</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,6 +1100,232 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129700507</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>308661</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6423857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127099409</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>308747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6423910</v>
+      </c>
+      <c r="S7" t="n">
+        <v>32</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Lundström, Maria Aronsson, tomas aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53008-2025 artfynd.xlsx
+++ b/artfynd/A 53008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700507</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,8 +1356,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127099409</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>